--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_375_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_375_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9263</v>
+        <v>5.9736</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7042</v>
+        <v>3.2638</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2222</v>
+        <v>2.7099</v>
       </c>
       <c r="G2" t="n">
         <v>2.8058</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5122</v>
+        <v>1.5595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3857</v>
+        <v>-0.0547</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1265</v>
+        <v>1.6142</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5072</v>
+        <v>4.5209</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1744</v>
+        <v>3.4234</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3327</v>
+        <v>1.0975</v>
       </c>
       <c r="G3" t="n">
         <v>1.2748</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6241</v>
+        <v>0.6379</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9752</v>
+        <v>0.2243</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6489</v>
+        <v>0.4136</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.873</v>
+        <v>3.8548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6647</v>
+        <v>1.4785</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2083</v>
+        <v>2.3764</v>
       </c>
       <c r="G4" t="n">
         <v>2.2303</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.749</v>
+        <v>0.2328</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2617</v>
+        <v>-0.4479</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5127</v>
+        <v>0.6807</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7336</v>
+        <v>2.5649</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1992</v>
+        <v>1.9633</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5345</v>
+        <v>0.6017</v>
       </c>
       <c r="G5" t="n">
         <v>0.7427</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8312</v>
+        <v>0.6625</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4182</v>
+        <v>0.4854</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.196</v>
+        <v>0.5917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.413</v>
+        <v>-0.4046</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.217</v>
+        <v>0.9963</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.697</v>
+        <v>-0.3321</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5894</v>
+        <v>0.7251</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1075</v>
+        <v>-1.0573</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8966</v>
+        <v>-0.043</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7359</v>
+        <v>0.1176</v>
       </c>
       <c r="L6" t="n">
         <v>-0.1607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8004</v>
+        <v>-0.2891</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1465</v>
+        <v>0.6075</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9469</v>
+        <v>-0.8966</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4112</v>
+        <v>-0.2359</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.3615</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1125</v>
+        <v>0.1256</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1467</v>
+        <v>0.3811</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.5309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8618</v>
+        <v>-0.1498</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3321</v>
+        <v>-1.697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7251</v>
+        <v>-0.5894</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0573</v>
+        <v>-1.1075</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.043</v>
+        <v>-0.8966</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1176</v>
+        <v>-0.7359</v>
       </c>
       <c r="L7" t="n">
         <v>-0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2891</v>
+        <v>-0.8004</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6075</v>
+        <v>0.1465</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8966</v>
+        <v>-0.9469</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.226</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>-0.1808</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3263</v>
+        <v>0.252</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3982</v>
+        <v>-0.4368</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.6888</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4559</v>
+        <v>-1.9883</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8824</v>
+        <v>-0.4693</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3383</v>
+        <v>-1.5191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4979</v>
+        <v>-1.5092</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6218</v>
+        <v>-0.0469</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1239</v>
+        <v>-1.4623</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9538</v>
+        <v>-0.4791</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2606</v>
+        <v>-0.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>-0.0568</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8162</v>
+        <v>0.7765</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>0.0002</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08</v>
+        <v>0.7762</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5251</v>
+        <v>0.1694</v>
       </c>
       <c r="E9" t="n">
-        <v>0.211</v>
+        <v>0.0303</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7361</v>
+        <v>0.1391</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4504</v>
+        <v>-0.4559</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2857</v>
+        <v>0.8824</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7361</v>
+        <v>-1.3383</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2857</v>
+        <v>0.4979</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2857</v>
+        <v>0.6218</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.1239</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7361</v>
+        <v>-0.9538</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2606</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7361</v>
+        <v>-1.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0747</v>
+        <v>-0.3205</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>-0.4676</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8829</v>
+        <v>-0.5251</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1012</v>
+        <v>0.211</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2183</v>
+        <v>-0.7361</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9883</v>
+        <v>-0.4504</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4693</v>
+        <v>0.2857</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5191</v>
+        <v>-0.7361</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5092</v>
+        <v>0.2857</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0469</v>
+        <v>0.2857</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4623</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4791</v>
+        <v>-0.7361</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4223</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0568</v>
+        <v>-0.7361</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3585</v>
+        <v>-0.0747</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6642</v>
+        <v>-0.0747</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3058</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9976</v>
+        <v>-1.0273</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4724</v>
+        <v>-1.8381</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4747</v>
+        <v>0.8108</v>
       </c>
       <c r="G11" t="n">
         <v>-4.328</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3304</v>
+        <v>0.3007</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2363</v>
+        <v>-0.1294</v>
       </c>
       <c r="U11" t="n">
-        <v>0.094</v>
+        <v>0.4301</v>
       </c>
       <c r="V11" t="n">
         <v>1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8986</v>
+        <v>-1.3796</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.753</v>
+        <v>-2.6037</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8544</v>
+        <v>1.2241</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6816</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2016</v>
+        <v>0.3174</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4753</v>
+        <v>-0.326</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2737</v>
+        <v>0.6434</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.9819</v>
+        <v>-6.4861</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.3024</v>
+        <v>-5.8738</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6795</v>
+        <v>-0.6123</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8671</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7257</v>
+        <v>-0.23</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>-0.2436</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0536</v>
+        <v>0.0136</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.770400000000003</v>
+        <v>8.890300000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.375900000000001</v>
+        <v>-0.2558000000000016</v>
       </c>
       <c r="F14" t="n">
-        <v>9.1462</v>
+        <v>9.146400000000002</v>
       </c>
       <c r="G14" t="n">
         <v>-5.746799999999999</v>
@@ -1519,7 +1519,7 @@
         <v>-13.4168</v>
       </c>
       <c r="J14" t="n">
-        <v>2.953</v>
+        <v>2.953000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>5.279399999999999</v>
@@ -1528,7 +1528,7 @@
         <v>-2.3266</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.6998</v>
+        <v>-8.699800000000002</v>
       </c>
       <c r="N14" t="n">
         <v>2.3908</v>
@@ -1546,19 +1546,19 @@
         <v>13.9173</v>
       </c>
       <c r="S14" t="n">
-        <v>2.280100000000001</v>
+        <v>3.4002</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.0049</v>
+        <v>-1.8847</v>
       </c>
       <c r="U14" t="n">
-        <v>5.2849</v>
+        <v>5.284800000000001</v>
       </c>
       <c r="V14" t="n">
         <v>7.757899999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>9.1137</v>
+        <v>9.113700000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-1.3558</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8786</v>
+        <v>3.3219</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2461</v>
+        <v>2.5714</v>
       </c>
       <c r="G15" t="n">
         <v>3.4546</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8079</v>
+        <v>-0.3646</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1123</v>
+        <v>-0.9944</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3044</v>
+        <v>0.6297</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0584</v>
+        <v>2.1087</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3472</v>
+        <v>0.2639</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7112000000000001</v>
+        <v>1.8448</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5925</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1211</v>
+        <v>0.4778</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7136</v>
+        <v>0.3413</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9898</v>
+        <v>0.2008</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3767</v>
+        <v>0.0168</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6132</v>
+        <v>0.184</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3973</v>
+        <v>0.6183</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4978</v>
+        <v>0.461</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1005</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2996</v>
+        <v>0.3618</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6247</v>
+        <v>0.063</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3251</v>
+        <v>0.2987</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6204</v>
+        <v>2.014</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09</v>
+        <v>1.3472</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7104</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8191000000000001</v>
+        <v>2.5925</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4778</v>
+        <v>-0.1211</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3413</v>
+        <v>2.7136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2008</v>
+        <v>2.9898</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0168</v>
+        <v>0.3767</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184</v>
+        <v>2.6132</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6183</v>
+        <v>-0.3973</v>
       </c>
       <c r="N17" t="n">
-        <v>0.461</v>
+        <v>-0.4978</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.1005</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1265</v>
+        <v>-0.344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2908</v>
+        <v>-0.6247</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1643</v>
+        <v>0.2807</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.214</v>
+        <v>-0.1809</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5605</v>
+        <v>-0.8838</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3465</v>
+        <v>0.7029</v>
       </c>
       <c r="G18" t="n">
-        <v>0.975</v>
+        <v>1.8821</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3767</v>
+        <v>-0.3697</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3517</v>
+        <v>2.2518</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8118</v>
+        <v>1.9073</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4033</v>
+        <v>0.0203</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4085</v>
+        <v>1.887</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8368</v>
+        <v>-0.0252</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.78</v>
+        <v>-0.39</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0568</v>
+        <v>0.3648</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6875</v>
+        <v>0.0246</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2513</v>
+        <v>-0.4716</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9388</v>
+        <v>0.4962</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4669</v>
+        <v>-0.2229</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0018</v>
+        <v>1.5605</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5349</v>
+        <v>-1.7834</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8821</v>
+        <v>0.975</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3697</v>
+        <v>-0.3767</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2518</v>
+        <v>1.3517</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9073</v>
+        <v>1.8118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0203</v>
+        <v>0.4033</v>
       </c>
       <c r="L19" t="n">
-        <v>1.887</v>
+        <v>1.4085</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0252</v>
+        <v>-0.8368</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.39</v>
+        <v>-0.78</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3648</v>
+        <v>-0.0568</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2614</v>
+        <v>0.2506</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5895</v>
+        <v>-0.2513</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3282</v>
+        <v>0.5019</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7513</v>
+        <v>-0.5496</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2351</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4839</v>
+        <v>0.6855</v>
       </c>
       <c r="G20" t="n">
         <v>1.1653</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1485</v>
+        <v>0.0532</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3189</v>
+        <v>0.5206</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2778</v>
+        <v>-1.3742</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7525</v>
+        <v>-2.3423</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4747</v>
+        <v>0.9681</v>
       </c>
       <c r="G21" t="n">
         <v>1.162</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1924</v>
+        <v>-0.2888</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2442</v>
+        <v>-0.3455</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4367</v>
+        <v>0.0567</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1823</v>
+        <v>-1.6775</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7865</v>
+        <v>-0.5506</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3958</v>
+        <v>-1.127</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5242</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3539</v>
+        <v>-0.8492</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4577</v>
+        <v>-0.1889</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5064</v>
+        <v>-2.332</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6915</v>
+        <v>-1.5736</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8149</v>
+        <v>-0.7585</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8977000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2324</v>
+        <v>-0.058</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3651</v>
+        <v>0.4215</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8103</v>
+        <v>-2.4571</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4406</v>
+        <v>-2.3226</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3697</v>
+        <v>-0.1344</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1273</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9871</v>
+        <v>-0.6339</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.315</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5468</v>
+        <v>-5.6343</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2247</v>
+        <v>-4.6965</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3221</v>
+        <v>-0.9378</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7545</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4422</v>
+        <v>0.3547</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0272</v>
+        <v>-0.4991</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4695</v>
+        <v>0.8538</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5387</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.7704</v>
+        <v>-6.9839</v>
       </c>
       <c r="E26" t="n">
         <v>-9.682400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9122</v>
+        <v>2.6984</v>
       </c>
       <c r="G26" t="n">
         <v>5.7469</v>
@@ -2473,7 +2473,7 @@
         <v>2.3264</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.479200000000001</v>
+        <v>-3.4792</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.9172</v>
@@ -2482,16 +2482,16 @@
         <v>10.438</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.28</v>
+        <v>-1.4936</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.2848</v>
+        <v>-5.285</v>
       </c>
       <c r="U26" t="n">
-        <v>3.0049</v>
+        <v>3.7912</v>
       </c>
       <c r="V26" t="n">
-        <v>-7.757899999999999</v>
+        <v>-7.757900000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0.8197000000000001</v>
